--- a/backend/data/financials_by_company/1682.HK.xlsx
+++ b/backend/data/financials_by_company/1682.HK.xlsx
@@ -3485,7 +3485,7 @@
         <v>-4812000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
         <v>1.471</v>
@@ -3673,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR2" t="n">
         <v>0.10113135</v>
